--- a/reports/rxkids_2028_flint/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028_flint/rxkids_2028_cost_and_impact.xlsx
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>51190891.1851922</v>
+        <v>49828007.31960575</v>
       </c>
     </row>
     <row r="9">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>59181214.65880781</v>
+        <v>60544098.52439427</v>
       </c>
     </row>
     <row r="10">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>2428669.748819335</v>
+        <v>3257170.578963077</v>
       </c>
     </row>
     <row r="11">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>33111631.7532</v>
+        <v>33111631.75320001</v>
       </c>
     </row>
     <row r="12">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>70362217.47555001</v>
+        <v>70362217.47555</v>
       </c>
     </row>
     <row r="13">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>239286</v>
+        <v>80867</v>
       </c>
     </row>
     <row r="29">
@@ -852,16 +852,16 @@
         <v>109745</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>7524</v>
+        <v>5242</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>15217514</v>
+        <v>11795556</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2023</v>
+        <v>2250</v>
       </c>
       <c r="G2" s="12" t="n">
-        <v>27.6</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="3">
@@ -877,16 +877,16 @@
         <v>109845</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>8207</v>
+        <v>7207</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>17715111</v>
+        <v>16214807</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>2159</v>
+        <v>2250</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>32.1</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="4">
@@ -902,16 +902,16 @@
         <v>109868</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>5753</v>
+        <v>8013</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>14639687</v>
+        <v>18029188</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2545</v>
+        <v>2250</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>26.5</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="5">
@@ -927,16 +927,16 @@
         <v>109862</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>2603</v>
+        <v>3681</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>6665893</v>
+        <v>8283335</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2561</v>
+        <v>2250</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>12.1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -952,16 +952,16 @@
         <v>109855</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>440</v>
+        <v>384</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>947850</v>
+        <v>863168</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>2154</v>
+        <v>2250</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>
@@ -1025,19 +1025,19 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>10800797</v>
+        <v>11111681</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>3393010</v>
+        <v>3703894</v>
       </c>
       <c r="D2" s="11" t="n">
         <v>7407787</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1065930</v>
+        <v>1517685</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>4731</v>
+        <v>4939</v>
       </c>
     </row>
     <row r="3">
@@ -1047,19 +1047,19 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>36138324</v>
+        <v>35675137</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>12354899</v>
+        <v>11891712</v>
       </c>
       <c r="D3" s="11" t="n">
         <v>23783425</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>1821886</v>
+        <v>2417015</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>16164</v>
+        <v>15856</v>
       </c>
     </row>
     <row r="4">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>2295306</v>
+        <v>2339773</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>735457</v>
+        <v>779924</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>1559849</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>425625</v>
+        <v>603000</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>1010</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="5">
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>5951627</v>
+        <v>6059462</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>1911985</v>
+        <v>2019821</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>4039641</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>717331</v>
+        <v>975764</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2621</v>
+        <v>2693</v>
       </c>
     </row>
   </sheetData>
@@ -1117,7 +1117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1162,192 +1162,179 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Prenatal unborn count</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
+          <t>Medicaid OR-clause</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Family-size increment for the prenatal FPL test</t>
+          <t>Clause 1: medicaid_receives from compute_medicaid_for_units</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Medicaid OR-clause</t>
+          <t>Prenatal payment</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>on</t>
+          <t>$1,500 × 1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Clause 1: medicaid_receives from compute_medicaid_for_units</t>
+          <t>One-time per pregnancy</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Prenatal payment</t>
+          <t>Postnatal payment</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$1,500 × 1</t>
+          <t>$500/mo × 6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>One-time per pregnancy</t>
+          <t>Per infant under cutoff</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Postnatal payment</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>$500/mo × 6</t>
-        </is>
+          <t>Take-up rate</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.98</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Per infant under cutoff</t>
+          <t>Combined eligibility×claim (Flint observed 0.98); swept for the band</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Take-up rate</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.98</v>
+          <t>Fertility response</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>+10%</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Combined eligibility×claim (Flint observed 0.98); swept for the band</t>
+          <t>Induced eligible-birth increase (Flint ~+10%); scales both arms</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fertility response</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>+10%</t>
-        </is>
+          <t>Birth rate / dependent</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.066</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Induced eligible-birth increase (Flint ~+10%); scales both arms</t>
+          <t>Annual births ÷ dependents (FLOW); drives both arms; swept ±25%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pregnancy probability (anchored)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.0521</v>
+          <t>Pregnancy Medicaid pathway</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.96× FPL</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Birth-anchored from raw 0.1 so expected pregnancies = eligible births; swept ±25%</t>
+          <t>Clause 1 prenatal pathway (196% FPL); subsumed by the 300% income test</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Child-under-age share</t>
+          <t>FPL table year</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.066</v>
+        <v>2028</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Annual births ÷ dependents (FLOW); postnatal infant proxy; swept ±25%</t>
+          <t>benefits/_fpl.py (2025 published; 2026-28 CPI-projected)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FPL table year</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2028</v>
+          <t>Tax treatment</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>non-taxable</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>benefits/_fpl.py (2025 published; 2026-28 CPI-projected)</t>
+          <t>Added to SPM resources only; no AGI/EITC/CTC interaction</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tax treatment</t>
+          <t>Fiscal weight</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>non-taxable</t>
+          <t>WGTP (household)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Added to SPM resources only; no AGI/EITC/CTC interaction</t>
+          <t>SPM-grain household weight; not the EITC-reweighted tax-unit weight</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fiscal weight</t>
+          <t>Income quintiles</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WGTP (household)</t>
+          <t>WGTP-weighted</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
-        <is>
-          <t>SPM-grain household weight; not the EITC-reweighted tax-unit weight</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Income quintiles</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>WGTP-weighted</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
         <is>
           <t>SPM units ranked on summed income; population-equal fifths</t>
         </is>

--- a/reports/rxkids_2028_flint/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028_flint/rxkids_2028_cost_and_impact.xlsx
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>55186052.92200001</v>
+        <v>54422457.01200001</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>18395350.974</v>
+        <v>18140819.004</v>
       </c>
     </row>
     <row r="7">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>36790701.948</v>
+        <v>36281638.008</v>
       </c>
     </row>
     <row r="8">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>49828007.31960575</v>
+        <v>49120467.84282387</v>
       </c>
     </row>
     <row r="9">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>60544098.52439427</v>
+        <v>59724446.18117615</v>
       </c>
     </row>
     <row r="10">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>3257170.578963077</v>
+        <v>3223093.719863913</v>
       </c>
     </row>
     <row r="11">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>33111631.75320001</v>
+        <v>32653474.20720001</v>
       </c>
     </row>
     <row r="12">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>70362217.47555</v>
+        <v>69388632.6903</v>
       </c>
     </row>
     <row r="13">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>36790701.948</v>
+        <v>36281638.008</v>
       </c>
     </row>
     <row r="16">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>91976754.87</v>
+        <v>90704095.02000001</v>
       </c>
     </row>
     <row r="17">
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>23079352.37941667</v>
+        <v>22760009.02816667</v>
       </c>
     </row>
     <row r="20">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>9964148.444250001</v>
+        <v>9826276.9605</v>
       </c>
     </row>
     <row r="21">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>13115203.93516667</v>
+        <v>12933732.06766667</v>
       </c>
     </row>
     <row r="22">
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>6813092.953333335</v>
+        <v>6718821.853333332</v>
       </c>
     </row>
     <row r="23">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>36024228.99075</v>
+        <v>35525770.5495</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>15386234.91961111</v>
+        <v>15173339.35211111</v>
       </c>
     </row>
     <row r="26">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>80867</v>
+        <v>79842</v>
       </c>
     </row>
     <row r="29">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>24527.134632</v>
+        <v>24187.758672</v>
       </c>
     </row>
     <row r="30">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>12263.567316</v>
+        <v>12093.879336</v>
       </c>
     </row>
     <row r="31">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>12263.567316</v>
+        <v>12093.879336</v>
       </c>
     </row>
     <row r="32">
@@ -861,7 +861,7 @@
         <v>2250</v>
       </c>
       <c r="G2" s="12" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="3">
@@ -886,7 +886,7 @@
         <v>2250</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>29.4</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="4">
@@ -902,16 +902,16 @@
         <v>109868</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>8013</v>
+        <v>7948</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>18029188</v>
+        <v>17883192</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>2250</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>32.7</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="5">
@@ -927,16 +927,16 @@
         <v>109862</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>3681</v>
+        <v>3536</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>8283335</v>
+        <v>7955805</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>2250</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>15</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="6">
@@ -952,16 +952,16 @@
         <v>109855</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>384</v>
+        <v>255</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>863168</v>
+        <v>573097</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>2250</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>
@@ -1025,19 +1025,19 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>11111681</v>
+        <v>11033561</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>3703894</v>
+        <v>3677854</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>7407787</v>
+        <v>7355707</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1517685</v>
+        <v>1505717</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>4939</v>
+        <v>4904</v>
       </c>
     </row>
     <row r="3">
@@ -1047,19 +1047,19 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>35675137</v>
+        <v>34989661</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>11891712</v>
+        <v>11663220</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>23783425</v>
+        <v>23326441</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>2417015</v>
+        <v>2426091</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>15856</v>
+        <v>15551</v>
       </c>
     </row>
     <row r="4">

--- a/reports/rxkids_2028_flint/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028_flint/rxkids_2028_cost_and_impact.xlsx
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>54422457.01200001</v>
+        <v>65158583.49000001</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>18140819.004</v>
+        <v>21719527.83</v>
       </c>
     </row>
     <row r="7">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>36281638.008</v>
+        <v>43439055.66</v>
       </c>
     </row>
     <row r="8">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>49120467.84282387</v>
+        <v>59931241.66318277</v>
       </c>
     </row>
     <row r="9">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>59724446.18117615</v>
+        <v>70385925.31681725</v>
       </c>
     </row>
     <row r="10">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>3223093.719863913</v>
+        <v>3177715.396241481</v>
       </c>
     </row>
     <row r="11">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>32653474.20720001</v>
+        <v>39095150.09400001</v>
       </c>
     </row>
     <row r="12">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>69388632.6903</v>
+        <v>83077193.94975002</v>
       </c>
     </row>
     <row r="13">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>36281638.008</v>
+        <v>43439055.66</v>
       </c>
     </row>
     <row r="16">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>90704095.02000001</v>
+        <v>108597639.15</v>
       </c>
     </row>
     <row r="17">
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>22760009.02816667</v>
+        <v>27249963.15708333</v>
       </c>
     </row>
     <row r="20">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>9826276.9605</v>
+        <v>11764744.24125</v>
       </c>
     </row>
     <row r="21">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>12933732.06766667</v>
+        <v>15485218.91583333</v>
       </c>
     </row>
     <row r="22">
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>6718821.853333332</v>
+        <v>8044269.566666666</v>
       </c>
     </row>
     <row r="23">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>35525770.5495</v>
+        <v>42534075.33374999</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>15173339.35211111</v>
+        <v>18166642.10472222</v>
       </c>
     </row>
     <row r="26">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>79842</v>
+        <v>95919</v>
       </c>
     </row>
     <row r="29">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>24187.758672</v>
+        <v>28959.37044</v>
       </c>
     </row>
     <row r="30">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>12093.879336</v>
+        <v>14479.68522</v>
       </c>
     </row>
     <row r="31">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>12093.879336</v>
+        <v>14479.68522</v>
       </c>
     </row>
     <row r="32">
@@ -861,7 +861,7 @@
         <v>2250</v>
       </c>
       <c r="G2" s="12" t="n">
-        <v>21.7</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="3">
@@ -886,7 +886,7 @@
         <v>2250</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>29.8</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="4">
@@ -902,16 +902,16 @@
         <v>109868</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>7948</v>
+        <v>7901</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>17883192</v>
+        <v>17777537</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>2250</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>32.9</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="5">
@@ -927,16 +927,16 @@
         <v>109862</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>3536</v>
+        <v>5070</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>7955805</v>
+        <v>11406554</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>2250</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>14.6</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="6">
@@ -952,16 +952,16 @@
         <v>109855</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>255</v>
+        <v>3540</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>573097</v>
+        <v>7964129</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>2250</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>1.1</v>
+        <v>12.2</v>
       </c>
     </row>
   </sheetData>
@@ -1025,19 +1025,19 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>11033561</v>
+        <v>12265880</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>3677854</v>
+        <v>4088627</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>7355707</v>
+        <v>8177253</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1505717</v>
+        <v>1427956</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>4904</v>
+        <v>5452</v>
       </c>
     </row>
     <row r="3">
@@ -1047,19 +1047,19 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>34989661</v>
+        <v>42980685</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>11663220</v>
+        <v>14326895</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>23326441</v>
+        <v>28653790</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>2426091</v>
+        <v>2526701</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>15551</v>
+        <v>19103</v>
       </c>
     </row>
     <row r="4">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>2339773</v>
+        <v>2688434</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>779924</v>
+        <v>896145</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>1559849</v>
+        <v>1792289</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>603000</v>
+        <v>616655</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>1040</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="5">
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>6059462</v>
+        <v>7223585</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2019821</v>
+        <v>2407862</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>4039641</v>
+        <v>4815724</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>975764</v>
+        <v>1004570</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2693</v>
+        <v>3210</v>
       </c>
     </row>
   </sheetData>

--- a/reports/rxkids_2028_flint/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028_flint/rxkids_2028_cost_and_impact.xlsx
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>8044269.566666666</v>
+        <v>8044269.566666668</v>
       </c>
     </row>
     <row r="23">
@@ -1351,7 +1351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1370,7 +1370,7 @@
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Cost = Σ (expected RxKids benefit × household weight) at SPM-unit grain. The benefit is already take-up- and pregnancy-probability-adjusted, so it is an expected annual dollar amount per unit, not a literal payment.</t>
+          <t>Both arms are driven by birth events (num_dependents × the annual birth rate per dependent); each eligible birth draws one prenatal + one postnatal payment. Cost = the take-up-adjusted benefit weighted by the household (WGTP) weight, summed to SPM-unit grain. Per-unit amounts are expectations, not literal payments.</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>Household impact here is the distribution of RxKids benefits RECEIVED across weighted income quintiles (SPM units ranked on summed income). This view does not use the tax engine or SPM poverty thresholds, so the whole run is genuine TY2028. A poverty-lift view (persons lifted) would require those engines, which stop at TY2025 — out of scope for this run.</t>
+          <t>Eligibility is tested on MAGI (gross income with 100% of Social Security) at the tax-unit / MAGI-household grain — the family Medicaid defines (42 CFR 435.603) — consistent with the statute's clause-1 Medicaid anchor. If the bill defines 'family' more broadly, the SPM-family grain (~$45M) is the alternative.</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>Sampling 90% CI is ACS sampling error only (SDR over 80 PUMS replicate weights). The assumption band is a one-at-a-time sweep over the three soft, unanchored parameters (take-up, pregnancy incidence, infant share) — cost is linear in each.</t>
+          <t>Household impact here is the distribution of RxKids benefits RECEIVED across weighted income quintiles (SPM units ranked on summed income). This view does not use the tax engine or SPM poverty thresholds, so the whole run is genuine TY2028. A poverty-lift view (persons lifted) would require those engines, which stop at TY2025 — out of scope for this run.</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>The base run prices the 6-month postnatal window (Flint's lower bound). The 'potential' line prices the optional extension to the full 12 months — the program may or may not opt in. Postnatal cost is linear in months, so the additional 6 months roughly equals the base postnatal arm again.</t>
+          <t>Sampling 90% CI is ACS sampling error only (SDR over 80 PUMS replicate weights). The assumption band is the joint (all-low/all-high corner) sweep over the two soft, unanchored drivers — take-up and the birth rate — cost is linear in each.</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>Caveats: 2026-2028 FPL is CPI-projected off the 2025 HHS table; pregnancy incidence and infant share are held at base-year values.</t>
+          <t>The base run prices the 6-month postnatal window (Flint's lower bound). The 'potential' line prices the optional extension to the full 12 months — the program may or may not opt in. Postnatal cost is linear in months, so the additional 6 months roughly equals the base postnatal arm again.</t>
         </is>
       </c>
     </row>
@@ -1419,6 +1419,16 @@
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Caveats: 2026-2028 FPL is CPI-projected off the 2025 HHS table; the birth rate is held at the base-year value (no 2028 birth-trend adjustment).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Full methodology: RXKIDS_METHODOLOGY.md (program origin, parameter sourcing, eligibility approximations, limitations).</t>
         </is>

--- a/reports/rxkids_2028_flint/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028_flint/rxkids_2028_cost_and_impact.xlsx
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>65158583.49000001</v>
+        <v>63421021.26360001</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>21719527.83</v>
+        <v>19981965.6036</v>
       </c>
     </row>
     <row r="7">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>59931241.66318277</v>
+        <v>58333075.21883123</v>
       </c>
     </row>
     <row r="9">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>70385925.31681725</v>
+        <v>68508967.30836879</v>
       </c>
     </row>
     <row r="10">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>3177715.396241481</v>
+        <v>3092976.319008377</v>
       </c>
     </row>
     <row r="11">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>39095150.09400001</v>
+        <v>38052945.19991251</v>
       </c>
     </row>
     <row r="12">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>83077193.94975002</v>
+        <v>80860915.59975001</v>
       </c>
     </row>
     <row r="13">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>43439055.66</v>
+        <v>43439055.65999998</v>
       </c>
     </row>
     <row r="16">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>108597639.15</v>
+        <v>106860076.9236</v>
       </c>
     </row>
     <row r="17">
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>27249963.15708333</v>
+        <v>26308783.61778333</v>
       </c>
     </row>
     <row r="20">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>11764744.24125</v>
+        <v>10823564.70195</v>
       </c>
     </row>
     <row r="21">
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>8044269.566666668</v>
+        <v>8044269.566666666</v>
       </c>
     </row>
     <row r="23">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>41.8</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="24">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>42534075.33374999</v>
+        <v>41158505.23785</v>
       </c>
     </row>
     <row r="25">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>18166642.10472222</v>
+        <v>17539189.07852222</v>
       </c>
     </row>
     <row r="26">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>28959.37044</v>
+        <v>27800.9956224</v>
       </c>
     </row>
     <row r="30">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>14479.68522</v>
+        <v>13321.3104024</v>
       </c>
     </row>
     <row r="31">
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>2250</v>
+        <v>2281.25</v>
       </c>
     </row>
     <row r="33">
@@ -852,13 +852,13 @@
         <v>109745</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>5242</v>
+        <v>5033</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>11795556</v>
+        <v>11481008</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2250</v>
+        <v>2281</v>
       </c>
       <c r="G2" s="12" t="n">
         <v>18.1</v>
@@ -877,13 +877,13 @@
         <v>109845</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>7207</v>
+        <v>6918</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>16214807</v>
+        <v>15782412</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>2250</v>
+        <v>2281</v>
       </c>
       <c r="G3" s="12" t="n">
         <v>24.9</v>
@@ -902,13 +902,13 @@
         <v>109868</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>7901</v>
+        <v>7585</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>17777537</v>
+        <v>17303470</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2250</v>
+        <v>2281</v>
       </c>
       <c r="G4" s="12" t="n">
         <v>27.3</v>
@@ -927,13 +927,13 @@
         <v>109862</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>5070</v>
+        <v>4867</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>11406554</v>
+        <v>11102379</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2250</v>
+        <v>2281</v>
       </c>
       <c r="G5" s="12" t="n">
         <v>17.5</v>
@@ -952,13 +952,13 @@
         <v>109855</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>3540</v>
+        <v>3398</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>7964129</v>
+        <v>7751752</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>2250</v>
+        <v>2281</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>12.2</v>
@@ -1025,19 +1025,19 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>12265880</v>
+        <v>11938790</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>4088627</v>
+        <v>3761536</v>
       </c>
       <c r="D2" s="11" t="n">
         <v>8177253</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1427956</v>
+        <v>1389877</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>5452</v>
+        <v>5233</v>
       </c>
     </row>
     <row r="3">
@@ -1047,19 +1047,19 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>42980685</v>
+        <v>41834533</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>14326895</v>
+        <v>13180743</v>
       </c>
       <c r="D3" s="11" t="n">
         <v>28653790</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>2526701</v>
+        <v>2459322</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>19103</v>
+        <v>18338</v>
       </c>
     </row>
     <row r="4">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>2688434</v>
+        <v>2616742</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>896145</v>
+        <v>824453</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>1792289</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>616655</v>
+        <v>600211</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>1195</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="5">
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>7223585</v>
+        <v>7030956</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2407862</v>
+        <v>2215233</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>4815724</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>1004570</v>
+        <v>977782</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>3210</v>
+        <v>3082</v>
       </c>
     </row>
   </sheetData>
@@ -1117,7 +1117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1213,7 +1213,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Take-up rate</t>
+          <t>Take-up — postnatal (newborn)</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1221,120 +1221,135 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Combined eligibility×claim (Flint observed 0.98); swept for the band</t>
+          <t>Flint observed 0.98; swept for the band</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fertility response</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>+10%</t>
-        </is>
+          <t>Take-up — prenatal</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.9016</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Induced eligible-birth increase (Flint ~+10%); scales both arms</t>
+          <t>0.92× postnatal (Flint: ~90% prenatal vs 98% newborn)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Birth rate / dependent</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.066</v>
+          <t>Fertility response</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>+10%</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Annual births ÷ dependents (FLOW); drives both arms; swept ±25%</t>
+          <t>Induced eligible-birth increase (Flint ~+10%); scales both arms</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pregnancy Medicaid pathway</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1.96× FPL</t>
-        </is>
+          <t>Birth rate / dependent</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.066</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Clause 1 prenatal pathway (196% FPL); subsumed by the 300% income test</t>
+          <t>Annual births ÷ dependents (FLOW); drives both arms; swept ±25%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FPL table year</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2028</v>
+          <t>Pregnancy Medicaid pathway</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1.96× FPL</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>benefits/_fpl.py (2025 published; 2026-28 CPI-projected)</t>
+          <t>Clause 1 prenatal pathway (196% FPL); subsumed by the 300% income test</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tax treatment</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>non-taxable</t>
-        </is>
+          <t>FPL table year</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2028</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Added to SPM resources only; no AGI/EITC/CTC interaction</t>
+          <t>benefits/_fpl.py (2025 published; 2026-28 CPI-projected)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Fiscal weight</t>
+          <t>Tax treatment</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WGTP (household)</t>
+          <t>non-taxable</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SPM-grain household weight; not the EITC-reweighted tax-unit weight</t>
+          <t>Added to SPM resources only; no AGI/EITC/CTC interaction</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Fiscal weight</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>WGTP (household)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SPM-grain household weight; not the EITC-reweighted tax-unit weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Income quintiles</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>WGTP-weighted</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>SPM units ranked on summed income; population-equal fifths</t>
         </is>

--- a/reports/rxkids_2028_flint/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028_flint/rxkids_2028_cost_and_impact.xlsx
@@ -10,8 +10,10 @@
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="By income quintile" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="By county" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Assumptions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Notes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="By scenario" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="County x scenario" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Assumptions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Notes" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -484,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -522,11 +524,11 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Total program cost</t>
+          <t>Total program cost (benefit)</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>63421021.26360001</v>
+        <v>37510868.70614231</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +538,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>19981965.6036</v>
+        <v>11818492.88001744</v>
       </c>
     </row>
     <row r="7">
@@ -546,234 +548,254 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>43439055.66</v>
+        <v>25692375.82612487</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Sampling 90% CI — low</t>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Administrative load (8%)</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>58333075.21883123</v>
+        <v>3000869.496491385</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Sampling 90% CI — high</t>
+          <t>Appropriation total (benefit + admin)</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>68508967.30836879</v>
+        <v>40511738.2026337</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  SDR standard error</t>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Sampling 90% CI — low</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>3092976.319008377</v>
+        <v>28149437.07310024</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
+          <t>Sampling 90% CI — high</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>46872300.33918439</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SDR standard error</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>5690839.89850582</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
           <t>Assumption band — low</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
-        <v>38052945.19991251</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="B13" s="6" t="n">
+        <v>22506717.84901059</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Assumption band — high</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
-        <v>80860915.59975001</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="B14" s="6" t="n">
+        <v>47825833.26613092</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>POTENTIAL — extend postnatal 6→12 months (optional)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Additional cost (+6 months)</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
-        <v>43439055.65999998</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="B17" s="6" t="n">
+        <v>25692375.82612487</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Total cost (12-month design)</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
-        <v>106860076.9236</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="B18" s="6" t="n">
+        <v>63203244.53226718</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>FIRST FISCAL YEAR (launch) — 12mo operating, 12mo ramp</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Year-1 disbursement (total)</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>26308783.61778333</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Prenatal</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>10823564.70195</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Postnatal</t>
+          <t xml:space="preserve">  Year-1 disbursement (total)</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>15485218.91583333</v>
+        <v>15560539.84061877</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    (postnatal deferred to next FY)</t>
+          <t xml:space="preserve">    Prenatal</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>8044269.566666666</v>
+        <v>6401683.643342781</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Year-1 as % of steady state</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="n">
-        <v>41.5</v>
+          <t xml:space="preserve">    Postnatal</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>9158856.197275994</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Year-1 if ramp = 6mo (fast)</t>
+          <t xml:space="preserve">    (postnatal deferred to next FY)</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>41158505.23785</v>
+        <v>4757847.375208311</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Year-1 as % of steady state</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Year-1 if ramp = 6mo (fast)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>24343526.09525331</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Year-1 if ramp = 18mo (slow)</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n">
-        <v>17539189.07852222</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="B27" s="6" t="n">
+        <v>10373693.22707918</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>HOUSEHOLD REACH</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Eligible families (weighted)</t>
         </is>
       </c>
-      <c r="B28" s="6" t="n">
-        <v>95919</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="B30" s="6" t="n">
+        <v>7340</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Expected recipients / year</t>
         </is>
       </c>
-      <c r="B29" s="6" t="n">
-        <v>27800.9956224</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="B31" s="6" t="n">
+        <v>16443.12052871992</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Expected pregnancies (prenatal)</t>
         </is>
       </c>
-      <c r="B30" s="6" t="n">
-        <v>13321.3104024</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="B32" s="6" t="n">
+        <v>7878.99525334496</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Expected infants (postnatal)</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n">
-        <v>14479.68522</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="B33" s="6" t="n">
+        <v>8564.125275374958</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Avg benefit per recipient</t>
         </is>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B34" s="6" t="n">
         <v>2281.25</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Benefits by income quintile → see the 'By income quintile' tab.</t>
         </is>
@@ -846,22 +868,22 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>17164</v>
+        <v>17182</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>109745</v>
+        <v>110267</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>5033</v>
+        <v>865</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>11481008</v>
+        <v>1973543</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G2" s="12" t="n">
-        <v>18.1</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="3">
@@ -871,22 +893,22 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>57695</v>
+        <v>57028</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>109845</v>
+        <v>110263</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>6918</v>
+        <v>5367</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>15782412</v>
+        <v>12242728</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>24.9</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="4">
@@ -896,22 +918,22 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>97780</v>
+        <v>96722</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>109868</v>
+        <v>110317</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>7585</v>
+        <v>5165</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>17303470</v>
+        <v>11783736</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>27.3</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="5">
@@ -921,22 +943,22 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>155996</v>
+        <v>154809</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>109862</v>
+        <v>110231</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>4867</v>
+        <v>3107</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>11102379</v>
+        <v>7086815</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>17.5</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="6">
@@ -946,22 +968,22 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>335998</v>
+        <v>334087</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>109855</v>
+        <v>110343</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>3398</v>
+        <v>1939</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>7751752</v>
+        <v>4424047</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>12.2</v>
+        <v>11.8</v>
       </c>
     </row>
   </sheetData>
@@ -1025,19 +1047,19 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>11938790</v>
+        <v>5430664</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>3761536</v>
+        <v>1711031</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>8177253</v>
+        <v>3719633</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1389877</v>
+        <v>1839250</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>5233</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="3">
@@ -1047,19 +1069,19 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>41834533</v>
+        <v>27447245</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>13180743</v>
+        <v>8647762</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>28653790</v>
+        <v>18799483</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>2459322</v>
+        <v>5125954</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>18338</v>
+        <v>12032</v>
       </c>
     </row>
     <row r="4">
@@ -1069,19 +1091,19 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>2616742</v>
+        <v>2840841</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>824453</v>
+        <v>895059</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>1792289</v>
+        <v>1945781</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>600211</v>
+        <v>1637854</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>1147</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="5">
@@ -1091,19 +1113,19 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>7030956</v>
+        <v>1792119</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2215233</v>
+        <v>564640</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>4815724</v>
+        <v>1227479</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>977782</v>
+        <v>885533</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>3082</v>
+        <v>786</v>
       </c>
     </row>
   </sheetData>
@@ -1117,242 +1139,246 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="B1" s="9" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C1" s="9" t="inlineStr">
-        <is>
-          <t>Notes</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Scenario comparison — take-up held constant (0.90 newborn / 0.83 prenatal); only eligibility + postnatal months differ</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Eligibility cap (income_fpl_cap)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>3.00× FPL</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Clause 2: 300% FPL income test</t>
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>Eligibility</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>Postnatal mo</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>$/birth</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>Cost total ($)</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>Prenatal ($)</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>Postnatal ($)</t>
+        </is>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>Admin ($)</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>Appropriation ($)</t>
+        </is>
+      </c>
+      <c r="J2" s="9" t="inlineStr">
+        <is>
+          <t>Band low ($)</t>
+        </is>
+      </c>
+      <c r="K2" s="9" t="inlineStr">
+        <is>
+          <t>Band high ($)</t>
+        </is>
+      </c>
+      <c r="L2" s="9" t="inlineStr">
+        <is>
+          <t>Expected recipients</t>
+        </is>
+      </c>
+      <c r="M2" s="9" t="inlineStr">
+        <is>
+          <t>Avg benefit ($)</t>
+        </is>
+      </c>
+      <c r="N2" s="9" t="inlineStr">
+        <is>
+          <t>First-year ($)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Medicaid OR-clause</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Clause 1: medicaid_receives from compute_medicaid_for_units</t>
-        </is>
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Medicaid OR ≤300% FPL</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>37510869</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>11818493</v>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>25692376</v>
+      </c>
+      <c r="H3" s="11" t="n">
+        <v>3000869</v>
+      </c>
+      <c r="I3" s="11" t="n">
+        <v>40511738</v>
+      </c>
+      <c r="J3" s="11" t="n">
+        <v>22506718</v>
+      </c>
+      <c r="K3" s="11" t="n">
+        <v>47825833</v>
+      </c>
+      <c r="L3" s="11" t="n">
+        <v>16443</v>
+      </c>
+      <c r="M3" s="11" t="n">
+        <v>2281</v>
+      </c>
+      <c r="N3" s="11" t="n">
+        <v>15560540</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Prenatal payment</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>$1,500 × 1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>One-time per pregnancy</t>
-        </is>
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 6-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Universal (no income/Medicaid test)</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>63874931</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>20124978</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>43749953</v>
+      </c>
+      <c r="H4" s="11" t="n">
+        <v>5109994</v>
+      </c>
+      <c r="I4" s="11" t="n">
+        <v>68984926</v>
+      </c>
+      <c r="J4" s="11" t="n">
+        <v>38325294</v>
+      </c>
+      <c r="K4" s="11" t="n">
+        <v>81439644</v>
+      </c>
+      <c r="L4" s="11" t="n">
+        <v>28000</v>
+      </c>
+      <c r="M4" s="11" t="n">
+        <v>2281</v>
+      </c>
+      <c r="N4" s="11" t="n">
+        <v>26497078</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Postnatal payment</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>$500/mo × 6</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Per infant under cutoff</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Take-up — postnatal (newborn)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Flint observed 0.98; swept for the band</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Take-up — prenatal</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.9016</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0.92× postnatal (Flint: ~90% prenatal vs 98% newborn)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Fertility response</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>+10%</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Induced eligible-birth increase (Flint ~+10%); scales both arms</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Birth rate / dependent</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Annual births ÷ dependents (FLOW); drives both arms; swept ±25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Pregnancy Medicaid pathway</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1.96× FPL</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Clause 1 prenatal pathway (196% FPL); subsumed by the 300% income test</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>FPL table year</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2028</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>benefits/_fpl.py (2025 published; 2026-28 CPI-projected)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Tax treatment</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>non-taxable</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Added to SPM resources only; no AGI/EITC/CTC interaction</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Fiscal weight</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>WGTP (household)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>SPM-grain household weight; not the EITC-reweighted tax-unit weight</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Income quintiles</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>WGTP-weighted</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>SPM units ranked on summed income; population-equal fifths</t>
-        </is>
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 12-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Universal (no income/Medicaid test)</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>107624884</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>20124978</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>87499906</v>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>8609991</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>116234875</v>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>64575265</v>
+      </c>
+      <c r="K5" s="11" t="n">
+        <v>137220834</v>
+      </c>
+      <c r="L5" s="11" t="n">
+        <v>28000</v>
+      </c>
+      <c r="M5" s="11" t="n">
+        <v>3844</v>
+      </c>
+      <c r="N5" s="11" t="n">
+        <v>29332723</v>
       </c>
     </row>
   </sheetData>
@@ -1366,7 +1392,676 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>County</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Cost total ($)</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Cost prenatal ($)</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Cost postnatal ($)</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Cost SE ($)</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>Expected recipients</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="n">
+        <v>5430664</v>
+      </c>
+      <c r="D2" s="11" t="n">
+        <v>1711031</v>
+      </c>
+      <c r="E2" s="11" t="n">
+        <v>3719633</v>
+      </c>
+      <c r="F2" s="11" t="n">
+        <v>1839250</v>
+      </c>
+      <c r="G2" s="11" t="n">
+        <v>2381</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Honolulu</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="n">
+        <v>27447245</v>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>8647762</v>
+      </c>
+      <c r="E3" s="11" t="n">
+        <v>18799483</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>5125954</v>
+      </c>
+      <c r="G3" s="11" t="n">
+        <v>12032</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Kauai</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="n">
+        <v>2840841</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>895059</v>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>1945781</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>1637854</v>
+      </c>
+      <c r="G4" s="11" t="n">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Maui</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>1792119</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>564640</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>1227479</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>885533</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 6-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>5430664</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>1711031</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>3719633</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>1839250</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>2381</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 6-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Honolulu</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>49381897</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>15558680</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>33823217</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>7648020</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>21647</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 6-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Kauai</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>2840841</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>895059</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>1945781</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>1637854</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 6-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Maui</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>6221529</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>1960208</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>4261321</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>3130447</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>2727</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 12-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>9150297</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>1711031</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>7439265</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>3099010</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>2381</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 12-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Honolulu</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>83205115</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>15558680</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>67646435</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>12886389</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>21647</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 12-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Kauai</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>4786622</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>895059</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>3891562</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>2759671</v>
+      </c>
+      <c r="G12" s="11" t="n">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 12-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Maui</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>10482851</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>1960208</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>8522643</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>5274590</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>2727</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Eligibility cap (income_fpl_cap)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>3.00× FPL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Clause 2: 300% FPL income test</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Medicaid OR-clause</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Clause 1: medicaid_receives from compute_medicaid_for_units</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Prenatal payment</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>$1,500 × 1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>One-time per pregnancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Postnatal payment</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>$500/mo × 6</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Per infant under cutoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Take-up — postnatal (newborn)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Flint observed 0.98; swept for the band</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Take-up — prenatal</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.9016</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.92× postnatal (Flint: ~90% prenatal vs 98% newborn)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Fertility response</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>+10%</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Induced eligible-birth increase (Flint ~+10%); scales both arms</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Birth driver</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>observed (age-0 deps)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Observed: age-0 dependents in PUMS, calibrated to NVSR; drives both arms; swept ±25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Birth cohort — base / target</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12,755 -&gt; 14,127</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NVSR 2022 basis; ensemble-projected to 2028</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Administrative load</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Operating overhead on benefit cost; separate appropriation line</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Pregnancy Medicaid pathway</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.96× FPL</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Clause 1 prenatal pathway (196% FPL); subsumed by the 300% income test</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FPL table year</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>benefits/_fpl.py (2025 published; 2026-28 CPI-projected)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Tax treatment</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>non-taxable</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Added to SPM resources only; no AGI/EITC/CTC interaction</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fiscal weight</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>WGTP (household)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SPM-grain household weight; not the EITC-reweighted tax-unit weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Income quintiles</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>WGTP-weighted</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SPM units ranked on summed income; population-equal fifths</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1385,7 +2080,7 @@
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Both arms are driven by birth events (num_dependents × the annual birth rate per dependent); each eligible birth draws one prenatal + one postnatal payment. Cost = the take-up-adjusted benefit weighted by the household (WGTP) weight, summed to SPM-unit grain. Per-unit amounts are expectations, not literal payments.</t>
+          <t>Both arms are driven by OBSERVED births — the count of age-0 dependents in each PUMS tax unit (an infant &lt;1yr ≈ a birth in the last 12 months, the annual flow). The weighted count is calibrated to CDC NVSR resident births (by-residence basis, 2022=15,535), then projected to 2028 with the repo's damped-trend ensemble (point 14,127, 90% PI [13,071, 15,183]). NVSR finals run through 2024; later years are nowcast from Hawaiʻi DOH preliminary births (snapshot 2026-07-06) converted occurrence→residence at ÷1.0055 (sd 0.0050, carried into their MOEs): 2025≈14,499; 2026≈14,374 (annualised from 5mo). Each birth draws one prenatal + one postnatal payment. This replaces the legacy num_dependents × rate proxy, which multiplied an all-dependents count (incl. older children, students, adult dependents) by a children-only-calibrated rate and overstated total births ~1.7×. Cost = the take-up-adjusted benefit weighted by the household (WGTP) weight, summed to SPM-unit grain. Per-unit amounts are expectations, not literal payments.</t>
         </is>
       </c>
     </row>
@@ -1415,7 +2110,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>Sampling 90% CI is ACS sampling error only (SDR over 80 PUMS replicate weights). The assumption band is the joint (all-low/all-high corner) sweep over the two soft, unanchored drivers — take-up and the birth rate — cost is linear in each.</t>
+          <t>Sampling 90% CI is ACS sampling error only (SDR over 80 PUMS replicate weights). The assumption band is the joint (all-low/all-high corner) sweep over the two soft drivers — take-up and the birth count (±25%) — cost is linear in each. The ±25% birth band comfortably covers the ensemble birth-projection's ~±23% 90% PI.</t>
         </is>
       </c>
     </row>
@@ -1425,7 +2120,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>The base run prices the 6-month postnatal window (Flint's lower bound). The 'potential' line prices the optional extension to the full 12 months — the program may or may not opt in. Postnatal cost is linear in months, so the additional 6 months roughly equals the base postnatal arm again.</t>
+          <t>The reported program cost is benefit dollars (cash out the door). The administrative line (8% of benefit) covers operating overhead (enrollment, disbursement, eligibility, outreach); the appropriation total is benefit + admin.</t>
         </is>
       </c>
     </row>
@@ -1435,7 +2130,7 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>Caveats: 2026-2028 FPL is CPI-projected off the 2025 HHS table; the birth rate is held at the base-year value (no 2028 birth-trend adjustment).</t>
+          <t>The base run prices the 6-month postnatal window (Flint's lower bound). The 'potential' line prices the optional extension to the full 12 months — the program may or may not opt in. Postnatal cost is linear in months, so the additional 6 months roughly equals the base postnatal arm again.</t>
         </is>
       </c>
     </row>
@@ -1444,6 +2139,16 @@
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Caveats: 2026-2028 FPL is CPI-projected off the 2025 HHS table. The birth cohort is projected with the ensemble (vital-statistics counts, not survey estimates); update HI_BIRTHS_BY_YEAR as new NVSR final-data releases land, and re-pull HI_DOH_BIRTHS_MONTHLY (bump DOH_SNAPSHOT) for the nowcast years. The occurrence-&gt;residence factor is calibrated on the post-2020 travel regime; a recovery toward the pre-COVID ~1.10 would make the nowcasts high.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Full methodology: RXKIDS_METHODOLOGY.md (program origin, parameter sourcing, eligibility approximations, limitations).</t>
         </is>

--- a/reports/rxkids_2028_flint/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028_flint/rxkids_2028_cost_and_impact.xlsx
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>37510868.70614231</v>
+        <v>38283149.62934565</v>
       </c>
     </row>
     <row r="6">
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>11818492.88001744</v>
+        <v>12061814.26678014</v>
       </c>
     </row>
     <row r="7">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>25692375.82612487</v>
+        <v>26221335.36256551</v>
       </c>
     </row>
     <row r="8">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>3000869.496491385</v>
+        <v>3062651.970347652</v>
       </c>
     </row>
     <row r="9">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>40511738.2026337</v>
+        <v>41345801.5996933</v>
       </c>
     </row>
     <row r="10">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>28149437.07310024</v>
+        <v>29042602.34573312</v>
       </c>
     </row>
     <row r="11">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>46872300.33918439</v>
+        <v>47523696.91295817</v>
       </c>
     </row>
     <row r="12">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>5690839.89850582</v>
+        <v>5617353.971800926</v>
       </c>
     </row>
     <row r="13">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>22506717.84901059</v>
+        <v>22970090.45109231</v>
       </c>
     </row>
     <row r="14">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>47825833.26613092</v>
+        <v>48810480.64812259</v>
       </c>
     </row>
     <row r="15">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>25692375.82612487</v>
+        <v>26221335.36256552</v>
       </c>
     </row>
     <row r="18">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>63203244.53226718</v>
+        <v>64504484.99191117</v>
       </c>
     </row>
     <row r="19">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>15560539.84061877</v>
+        <v>15880903.20430935</v>
       </c>
     </row>
     <row r="22">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>6401683.643342781</v>
+        <v>6533482.727839241</v>
       </c>
     </row>
     <row r="23">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>9158856.197275994</v>
+        <v>9347420.476470113</v>
       </c>
     </row>
     <row r="24">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>4757847.375208311</v>
+        <v>4855802.84491954</v>
       </c>
     </row>
     <row r="25">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>24343526.09525331</v>
+        <v>24844715.25603083</v>
       </c>
     </row>
     <row r="27">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>10373693.22707918</v>
+        <v>10587268.8028729</v>
       </c>
     </row>
     <row r="28">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>16443.12052871992</v>
+        <v>16781.65463204193</v>
       </c>
     </row>
     <row r="32">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>7878.99525334496</v>
+        <v>8041.209511186757</v>
       </c>
     </row>
     <row r="33">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>8564.125275374958</v>
+        <v>8740.445120855173</v>
       </c>
     </row>
     <row r="34">
@@ -874,16 +874,16 @@
         <v>110267</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>865</v>
+        <v>924</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1973543</v>
+        <v>2108586</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G2" s="12" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="3">
@@ -893,22 +893,22 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>57028</v>
+        <v>57026</v>
       </c>
       <c r="C3" s="11" t="n">
         <v>110263</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>5367</v>
+        <v>5604</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>12242728</v>
+        <v>12784767</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>32.6</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="4">
@@ -924,16 +924,16 @@
         <v>110317</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>5165</v>
+        <v>5030</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>11783736</v>
+        <v>11475307</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>31.4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -949,16 +949,16 @@
         <v>110231</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>3107</v>
+        <v>3280</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>7086815</v>
+        <v>7482913</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>18.9</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="6">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>334087</v>
+        <v>334084</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>110343</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1939</v>
+        <v>1943</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>4424047</v>
+        <v>4431577</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
     </row>
   </sheetData>
@@ -1047,19 +1047,19 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>5430664</v>
+        <v>7644254</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1711031</v>
+        <v>2408463</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>3719633</v>
+        <v>5235790</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1839250</v>
+        <v>2588945</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2381</v>
+        <v>3351</v>
       </c>
     </row>
     <row r="3">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>27447245</v>
+        <v>26237303</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>8647762</v>
+        <v>8266548</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>18799483</v>
+        <v>17970756</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>5125954</v>
+        <v>4899989</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>12032</v>
+        <v>11501</v>
       </c>
     </row>
     <row r="4">
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>2840841</v>
+        <v>2601356</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>895059</v>
+        <v>819605</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>1945781</v>
+        <v>1781751</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>1637854</v>
+        <v>1499782</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>1245</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="5">
@@ -1113,19 +1113,19 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>1792119</v>
+        <v>1800237</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>564640</v>
+        <v>567198</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>1227479</v>
+        <v>1233039</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>885533</v>
+        <v>887055</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>786</v>
+        <v>789</v>
       </c>
     </row>
   </sheetData>
@@ -1255,34 +1255,34 @@
         <v>4500</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>37510869</v>
+        <v>38283150</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>11818493</v>
+        <v>12061814</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>25692376</v>
+        <v>26221335</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>3000869</v>
+        <v>3062652</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>40511738</v>
+        <v>41345802</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>22506718</v>
+        <v>22970090</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>47825833</v>
+        <v>48810481</v>
       </c>
       <c r="L3" s="11" t="n">
-        <v>16443</v>
+        <v>16782</v>
       </c>
       <c r="M3" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="N3" s="11" t="n">
-        <v>15560540</v>
+        <v>15880903</v>
       </c>
     </row>
     <row r="4">
@@ -1303,34 +1303,34 @@
         <v>4500</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>63874931</v>
+        <v>63793115</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>20124978</v>
+        <v>20099201</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>43749953</v>
+        <v>43693914</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>5109994</v>
+        <v>5103449</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>68984926</v>
+        <v>68896564</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>38325294</v>
+        <v>38276203</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>81439644</v>
+        <v>81335329</v>
       </c>
       <c r="L4" s="11" t="n">
-        <v>28000</v>
+        <v>27964</v>
       </c>
       <c r="M4" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="N4" s="11" t="n">
-        <v>26497078</v>
+        <v>26463138</v>
       </c>
     </row>
     <row r="5">
@@ -1351,34 +1351,34 @@
         <v>7500</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>107624884</v>
+        <v>107487029</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>20124978</v>
+        <v>20099201</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>87499906</v>
+        <v>87387828</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>8609991</v>
+        <v>8598962</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>116234875</v>
+        <v>116085991</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>64575265</v>
+        <v>64492552</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>137220834</v>
+        <v>137045070</v>
       </c>
       <c r="L5" s="11" t="n">
-        <v>28000</v>
+        <v>27964</v>
       </c>
       <c r="M5" s="11" t="n">
         <v>3844</v>
       </c>
       <c r="N5" s="11" t="n">
-        <v>29332723</v>
+        <v>29295151</v>
       </c>
     </row>
   </sheetData>
@@ -1453,19 +1453,19 @@
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>5430664</v>
+        <v>7644254</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>1711031</v>
+        <v>2408463</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>3719633</v>
+        <v>5235790</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>1839250</v>
+        <v>2588945</v>
       </c>
       <c r="G2" s="11" t="n">
-        <v>2381</v>
+        <v>3351</v>
       </c>
     </row>
     <row r="3">
@@ -1480,19 +1480,19 @@
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>27447245</v>
+        <v>26237303</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>8647762</v>
+        <v>8266548</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>18799483</v>
+        <v>17970756</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>5125954</v>
+        <v>4899989</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>12032</v>
+        <v>11501</v>
       </c>
     </row>
     <row r="4">
@@ -1507,19 +1507,19 @@
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2840841</v>
+        <v>2601356</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>895059</v>
+        <v>819605</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>1945781</v>
+        <v>1781751</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>1637854</v>
+        <v>1499782</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>1245</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="5">
@@ -1534,19 +1534,19 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>1792119</v>
+        <v>1800237</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>564640</v>
+        <v>567198</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>1227479</v>
+        <v>1233039</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>885533</v>
+        <v>887055</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>786</v>
+        <v>789</v>
       </c>
     </row>
     <row r="6">
@@ -1561,19 +1561,19 @@
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>5430664</v>
+        <v>7644254</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1711031</v>
+        <v>2408463</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>3719633</v>
+        <v>5235790</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1839250</v>
+        <v>2588945</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>2381</v>
+        <v>3351</v>
       </c>
     </row>
     <row r="7">
@@ -1588,19 +1588,19 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>49381897</v>
+        <v>47205022</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>15558680</v>
+        <v>14872815</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>33823217</v>
+        <v>32332207</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>7648020</v>
+        <v>7310876</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>21647</v>
+        <v>20693</v>
       </c>
     </row>
     <row r="8">
@@ -1615,19 +1615,19 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>2840841</v>
+        <v>2601356</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>895059</v>
+        <v>819605</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1945781</v>
+        <v>1781751</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1637854</v>
+        <v>1499782</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>1245</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="9">
@@ -1642,19 +1642,19 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>6221529</v>
+        <v>6342483</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1960208</v>
+        <v>1998316</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>4261321</v>
+        <v>4344166</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>3130447</v>
+        <v>3202331</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>2727</v>
+        <v>2780</v>
       </c>
     </row>
     <row r="10">
@@ -1669,19 +1669,19 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>9150297</v>
+        <v>12880044</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>1711031</v>
+        <v>2408463</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>7439265</v>
+        <v>10471580</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3099010</v>
+        <v>4362196</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>2381</v>
+        <v>3351</v>
       </c>
     </row>
     <row r="11">
@@ -1696,19 +1696,19 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>83205115</v>
+        <v>79537229</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>15558680</v>
+        <v>14872815</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>67646435</v>
+        <v>64664414</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>12886389</v>
+        <v>12318325</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>21647</v>
+        <v>20693</v>
       </c>
     </row>
     <row r="12">
@@ -1723,19 +1723,19 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>4786622</v>
+        <v>4383107</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>895059</v>
+        <v>819605</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>3891562</v>
+        <v>3563502</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>2759671</v>
+        <v>2527030</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>1245</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="13">
@@ -1750,19 +1750,19 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>10482851</v>
+        <v>10686649</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>1960208</v>
+        <v>1998316</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>8522643</v>
+        <v>8688332</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5274590</v>
+        <v>5395708</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>2727</v>
+        <v>2780</v>
       </c>
     </row>
   </sheetData>
@@ -2080,7 +2080,7 @@
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Both arms are driven by OBSERVED births — the count of age-0 dependents in each PUMS tax unit (an infant &lt;1yr ≈ a birth in the last 12 months, the annual flow). The weighted count is calibrated to CDC NVSR resident births (by-residence basis, 2022=15,535), then projected to 2028 with the repo's damped-trend ensemble (point 14,127, 90% PI [13,071, 15,183]). NVSR finals run through 2024; later years are nowcast from Hawaiʻi DOH preliminary births (snapshot 2026-07-06) converted occurrence→residence at ÷1.0055 (sd 0.0050, carried into their MOEs): 2025≈14,499; 2026≈14,374 (annualised from 5mo). Each birth draws one prenatal + one postnatal payment. This replaces the legacy num_dependents × rate proxy, which multiplied an all-dependents count (incl. older children, students, adult dependents) by a children-only-calibrated rate and overstated total births ~1.7×. Cost = the take-up-adjusted benefit weighted by the household (WGTP) weight, summed to SPM-unit grain. Per-unit amounts are expectations, not literal payments.</t>
+          <t>Both arms are driven by OBSERVED births — the count of age-0 dependents in each PUMS tax unit (an infant &lt;1yr ≈ a birth in the last 12 months, the annual flow). The weighted count is calibrated to CDC NVSR resident births (by-residence basis, 2022=15,535), then projected to 2028 with the repo's damped-trend ensemble (point 14,127, 90% PI [13,071, 15,183]). NVSR finals run through 2024; later years are nowcast from Hawaiʻi DOH preliminary births (snapshot 2026-07-06) converted occurrence→residence at ÷1.0055 (sd 0.0050, carried into their MOEs): 2025≈14,499; 2026≈14,374 (annualised from 5mo). Each birth draws one prenatal + one postnatal payment. This replaces the legacy num_dependents × rate proxy, which multiplied an all-dependents count (incl. older children, students, adult dependents) by a children-only-calibrated rate and overstated total births ~1.7×. County split: recalibrated to Hawaiʻi DOH's aggregate county vital-statistics shares (2018-2025), not raw PUMS county shares — PUMS's own county allocation is small-sample-noisy (Hawaii County carries only ~11 sampled infants) and Maui/Kauai are not independently sampled at all (one combined PUMA, split by a demographic-heuristic imputer, not survey evidence). Per-county factor vs the raw PUMS-implied count: Honolulu×0.96; Hawaii×1.41; Maui×1.03; Kauai×0.92. The state BIRTH total is unchanged (redistribution only), but the state COST total is NOT — eligibility is unit-specific and correlated with county, so this also corrects the eligible share (measured +2.1% on cost/recipients on the real frame; eligible_families itself is unchanged). --no-doh-county-shares restores raw PUMS shares. Cost = the take-up-adjusted benefit weighted by the household (WGTP) weight, summed to SPM-unit grain. Per-unit amounts are expectations, not literal payments.</t>
         </is>
       </c>
     </row>

--- a/reports/rxkids_2028_flint/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028_flint/rxkids_2028_cost_and_impact.xlsx
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>38283149.62934565</v>
+        <v>38398620.42325183</v>
       </c>
     </row>
     <row r="6">
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>12061814.26678014</v>
+        <v>12098195.47581907</v>
       </c>
     </row>
     <row r="7">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>26221335.36256551</v>
+        <v>26300424.94743276</v>
       </c>
     </row>
     <row r="8">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>3062651.970347652</v>
+        <v>3071889.633860147</v>
       </c>
     </row>
     <row r="9">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>41345801.5996933</v>
+        <v>41470510.05711198</v>
       </c>
     </row>
     <row r="10">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>29042602.34573312</v>
+        <v>29183663.96675771</v>
       </c>
     </row>
     <row r="11">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>47523696.91295817</v>
+        <v>47613576.87974595</v>
       </c>
     </row>
     <row r="12">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>5617353.971800926</v>
+        <v>5601797.23799035</v>
       </c>
     </row>
     <row r="13">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>22970090.45109231</v>
+        <v>23039373.53271345</v>
       </c>
     </row>
     <row r="14">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>48810480.64812259</v>
+        <v>48957704.29627982</v>
       </c>
     </row>
     <row r="15">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>26221335.36256552</v>
+        <v>26300424.94743276</v>
       </c>
     </row>
     <row r="18">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>64504484.99191117</v>
+        <v>64699045.37068459</v>
       </c>
     </row>
     <row r="19">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>15880903.20430935</v>
+        <v>15928803.66492201</v>
       </c>
     </row>
     <row r="22">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>6533482.727839241</v>
+        <v>6553189.216068663</v>
       </c>
     </row>
     <row r="23">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>9347420.476470113</v>
+        <v>9375614.448853346</v>
       </c>
     </row>
     <row r="24">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>4855802.84491954</v>
+        <v>4870449.064339399</v>
       </c>
     </row>
     <row r="25">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>24844715.25603083</v>
+        <v>24919652.63769254</v>
       </c>
     </row>
     <row r="27">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>10587268.8028729</v>
+        <v>10619202.44328134</v>
       </c>
     </row>
     <row r="28">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>16781.65463204193</v>
+        <v>16832.27196635697</v>
       </c>
     </row>
     <row r="32">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>8041.209511186757</v>
+        <v>8065.463650546046</v>
       </c>
     </row>
     <row r="33">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>8740.445120855173</v>
+        <v>8766.808315810922</v>
       </c>
     </row>
     <row r="34">
@@ -868,16 +868,16 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>17182</v>
+        <v>17179</v>
       </c>
       <c r="C2" s="11" t="n">
         <v>110267</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2108586</v>
+        <v>2121077</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>2281</v>
@@ -899,16 +899,16 @@
         <v>110263</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>5604</v>
+        <v>5611</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>12784767</v>
+        <v>12801188</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="4">
@@ -924,16 +924,16 @@
         <v>110317</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>5030</v>
+        <v>4962</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>11475307</v>
+        <v>11319157</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>30</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="5">
@@ -949,16 +949,16 @@
         <v>110231</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>3280</v>
+        <v>3397</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>7482913</v>
+        <v>7749476</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>19.5</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="6">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>334084</v>
+        <v>334087</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>110343</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1943</v>
+        <v>1932</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>4431577</v>
+        <v>4407722</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
     </row>
   </sheetData>
@@ -1047,19 +1047,19 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>7644254</v>
+        <v>8303727</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>2408463</v>
+        <v>2616243</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>5235790</v>
+        <v>5687484</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2588945</v>
+        <v>2812295</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>3351</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="3">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>26237303</v>
+        <v>25363059</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>8266548</v>
+        <v>7991101</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>17970756</v>
+        <v>17371958</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>4899989</v>
+        <v>4736718</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>11501</v>
+        <v>11118</v>
       </c>
     </row>
     <row r="4">
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>2601356</v>
+        <v>2741393</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>819605</v>
+        <v>863727</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>1781751</v>
+        <v>1877667</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>1499782</v>
+        <v>1580519</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>1140</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="5">
@@ -1113,19 +1113,19 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>1800237</v>
+        <v>1990442</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>567198</v>
+        <v>627126</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>1233039</v>
+        <v>1363316</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>887055</v>
+        <v>980027</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>789</v>
+        <v>873</v>
       </c>
     </row>
   </sheetData>
@@ -1255,34 +1255,34 @@
         <v>4500</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>38283150</v>
+        <v>38398620</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>12061814</v>
+        <v>12098195</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>26221335</v>
+        <v>26300425</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>3062652</v>
+        <v>3071890</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>41345802</v>
+        <v>41470510</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>22970090</v>
+        <v>23039374</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>48810481</v>
+        <v>48957704</v>
       </c>
       <c r="L3" s="11" t="n">
-        <v>16782</v>
+        <v>16832</v>
       </c>
       <c r="M3" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="N3" s="11" t="n">
-        <v>15880903</v>
+        <v>15928804</v>
       </c>
     </row>
     <row r="4">
@@ -1303,34 +1303,34 @@
         <v>4500</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>63793115</v>
+        <v>63739402</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>20099201</v>
+        <v>20082277</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>43693914</v>
+        <v>43657125</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>5103449</v>
+        <v>5099152</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>68896564</v>
+        <v>68838555</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>38276203</v>
+        <v>38243976</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>81335329</v>
+        <v>81266847</v>
       </c>
       <c r="L4" s="11" t="n">
-        <v>27964</v>
+        <v>27941</v>
       </c>
       <c r="M4" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="N4" s="11" t="n">
-        <v>26463138</v>
+        <v>26440857</v>
       </c>
     </row>
     <row r="5">
@@ -1351,34 +1351,34 @@
         <v>7500</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>107487029</v>
+        <v>107396527</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>20099201</v>
+        <v>20082277</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>87387828</v>
+        <v>87314250</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>8598962</v>
+        <v>8591722</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>116085991</v>
+        <v>115988249</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>64492552</v>
+        <v>64438250</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>137045070</v>
+        <v>136929681</v>
       </c>
       <c r="L5" s="11" t="n">
-        <v>27964</v>
+        <v>27941</v>
       </c>
       <c r="M5" s="11" t="n">
         <v>3844</v>
       </c>
       <c r="N5" s="11" t="n">
-        <v>29295151</v>
+        <v>29270485</v>
       </c>
     </row>
   </sheetData>
@@ -1453,19 +1453,19 @@
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>7644254</v>
+        <v>8303727</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2408463</v>
+        <v>2616243</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>5235790</v>
+        <v>5687484</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2588945</v>
+        <v>2812295</v>
       </c>
       <c r="G2" s="11" t="n">
-        <v>3351</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="3">
@@ -1480,19 +1480,19 @@
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>26237303</v>
+        <v>25363059</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>8266548</v>
+        <v>7991101</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>17970756</v>
+        <v>17371958</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>4899989</v>
+        <v>4736718</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>11501</v>
+        <v>11118</v>
       </c>
     </row>
     <row r="4">
@@ -1507,19 +1507,19 @@
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2601356</v>
+        <v>2741393</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>819605</v>
+        <v>863727</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>1781751</v>
+        <v>1877667</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>1499782</v>
+        <v>1580519</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>1140</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="5">
@@ -1534,19 +1534,19 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>1800237</v>
+        <v>1990442</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>567198</v>
+        <v>627126</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>1233039</v>
+        <v>1363316</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>887055</v>
+        <v>980027</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>789</v>
+        <v>873</v>
       </c>
     </row>
     <row r="6">
@@ -1561,19 +1561,19 @@
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>7644254</v>
+        <v>8303727</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>2408463</v>
+        <v>2616243</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>5235790</v>
+        <v>5687484</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>2588945</v>
+        <v>2812295</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>3351</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="7">
@@ -1588,19 +1588,19 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>47205022</v>
+        <v>45632119</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>14872815</v>
+        <v>14377243</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>32332207</v>
+        <v>31254876</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>7310876</v>
+        <v>7067273</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>20693</v>
+        <v>20003</v>
       </c>
     </row>
     <row r="8">
@@ -1615,19 +1615,19 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>2601356</v>
+        <v>2741393</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>819605</v>
+        <v>863727</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1781751</v>
+        <v>1877667</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1499782</v>
+        <v>1580519</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>1140</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="9">
@@ -1642,19 +1642,19 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>6342483</v>
+        <v>7062164</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1998316</v>
+        <v>2225065</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>4344166</v>
+        <v>4837098</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>3202331</v>
+        <v>3571707</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>2780</v>
+        <v>3096</v>
       </c>
     </row>
     <row r="10">
@@ -1669,19 +1669,19 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>12880044</v>
+        <v>13991211</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>2408463</v>
+        <v>2616243</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>10471580</v>
+        <v>11374968</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>4362196</v>
+        <v>4738524</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>3351</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="11">
@@ -1696,19 +1696,19 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>79537229</v>
+        <v>76886995</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>14872815</v>
+        <v>14377243</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>64664414</v>
+        <v>62509752</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>12318325</v>
+        <v>11907870</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>20693</v>
+        <v>20003</v>
       </c>
     </row>
     <row r="12">
@@ -1723,19 +1723,19 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>4383107</v>
+        <v>4619060</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>819605</v>
+        <v>863727</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>3563502</v>
+        <v>3755333</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>2527030</v>
+        <v>2663065</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>1140</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="13">
@@ -1750,19 +1750,19 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>10686649</v>
+        <v>11899262</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>1998316</v>
+        <v>2225065</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>8688332</v>
+        <v>9674197</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5395708</v>
+        <v>6018081</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>2780</v>
+        <v>3096</v>
       </c>
     </row>
   </sheetData>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12,755 -&gt; 14,127</t>
+          <t>12,755 -&gt; 14,126</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2080,7 +2080,7 @@
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Both arms are driven by OBSERVED births — the count of age-0 dependents in each PUMS tax unit (an infant &lt;1yr ≈ a birth in the last 12 months, the annual flow). The weighted count is calibrated to CDC NVSR resident births (by-residence basis, 2022=15,535), then projected to 2028 with the repo's damped-trend ensemble (point 14,127, 90% PI [13,071, 15,183]). NVSR finals run through 2024; later years are nowcast from Hawaiʻi DOH preliminary births (snapshot 2026-07-06) converted occurrence→residence at ÷1.0055 (sd 0.0050, carried into their MOEs): 2025≈14,499; 2026≈14,374 (annualised from 5mo). Each birth draws one prenatal + one postnatal payment. This replaces the legacy num_dependents × rate proxy, which multiplied an all-dependents count (incl. older children, students, adult dependents) by a children-only-calibrated rate and overstated total births ~1.7×. County split: recalibrated to Hawaiʻi DOH's aggregate county vital-statistics shares (2018-2025), not raw PUMS county shares — PUMS's own county allocation is small-sample-noisy (Hawaii County carries only ~11 sampled infants) and Maui/Kauai are not independently sampled at all (one combined PUMA, split by a demographic-heuristic imputer, not survey evidence). Per-county factor vs the raw PUMS-implied count: Honolulu×0.96; Hawaii×1.41; Maui×1.03; Kauai×0.92. The state BIRTH total is unchanged (redistribution only), but the state COST total is NOT — eligibility is unit-specific and correlated with county, so this also corrects the eligible share (measured +2.1% on cost/recipients on the real frame; eligible_families itself is unchanged). --no-doh-county-shares restores raw PUMS shares. Cost = the take-up-adjusted benefit weighted by the household (WGTP) weight, summed to SPM-unit grain. Per-unit amounts are expectations, not literal payments.</t>
+          <t>Both arms are driven by OBSERVED births — the count of age-0 dependents in each PUMS tax unit (an infant &lt;1yr ≈ a birth in the last 12 months, the annual flow). The weighted count is calibrated to CDC NVSR resident births (by-residence basis, 2022=15,535), then projected to 2028 with the repo's damped-trend ensemble (point 14,126, 90% PI [12,868, 15,384]). NVSR finals run through 2024; later years are nowcast from Hawaiʻi DOH preliminary births (snapshot 2026-07-06) converted occurrence→residence at ÷1.0026 (sd 0.0007, carried into their MOEs): 2025≈14,541; 2026≈14,416 (annualised from 5mo). Each birth draws one prenatal + one postnatal payment. This replaces the legacy num_dependents × rate proxy, which multiplied an all-dependents count (incl. older children, students, adult dependents) by a children-only-calibrated rate and overstated total births ~1.7×. County split: recalibrated to CDC WONDER county-of-RESIDENCE natality shares (2020-2024), not raw PUMS county shares — PUMS's own county allocation is small-sample-noisy (Hawaii County carries only ~11 sampled infants) and Maui/Kauai are not independently sampled at all (one combined PUMA, split by a demographic-heuristic imputer, not survey evidence). Residence basis matters here: DOH's occurrence counts overstate Honolulu ~2.2pp because neighbour-island mothers deliver on Oʻahu. Per-county factor vs the raw PUMS-implied count: Honolulu×0.92; Hawaii×1.53; Maui×1.15; Kauai×0.97. The state BIRTH total is unchanged (redistribution only), but the state COST total is NOT — eligibility is unit-specific and correlated with county, so this also corrects the eligible share (eligible_families itself is unchanged). --no-county-share-calibration restores raw PUMS shares. Cost = the take-up-adjusted benefit weighted by the household (WGTP) weight, summed to SPM-unit grain. Per-unit amounts are expectations, not literal payments.</t>
         </is>
       </c>
     </row>

--- a/reports/rxkids_2028_flint/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028_flint/rxkids_2028_cost_and_impact.xlsx
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>38398620.42325183</v>
+        <v>37626973.80405268</v>
       </c>
     </row>
     <row r="6">
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>12098195.47581907</v>
+        <v>11855073.93826317</v>
       </c>
     </row>
     <row r="7">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>26300424.94743276</v>
+        <v>25771899.8657895</v>
       </c>
     </row>
     <row r="8">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>3071889.633860147</v>
+        <v>3010157.904324214</v>
       </c>
     </row>
     <row r="9">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>41470510.05711198</v>
+        <v>40637131.70837689</v>
       </c>
     </row>
     <row r="10">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>29183663.96675771</v>
+        <v>28597198.2190936</v>
       </c>
     </row>
     <row r="11">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>47613576.87974595</v>
+        <v>46656749.38901176</v>
       </c>
     </row>
     <row r="12">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>5601797.23799035</v>
+        <v>5489225.279610383</v>
       </c>
     </row>
     <row r="13">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>23039373.53271345</v>
+        <v>22576381.51635915</v>
       </c>
     </row>
     <row r="14">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>48957704.29627982</v>
+        <v>47973865.64302704</v>
       </c>
     </row>
     <row r="15">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>26300424.94743276</v>
+        <v>25771899.8657895</v>
       </c>
     </row>
     <row r="18">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>64699045.37068459</v>
+        <v>63398873.66984218</v>
       </c>
     </row>
     <row r="19">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>15928803.66492201</v>
+        <v>15608703.42797492</v>
       </c>
     </row>
     <row r="22">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>6553189.216068663</v>
+        <v>6421498.383225884</v>
       </c>
     </row>
     <row r="23">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>9375614.448853346</v>
+        <v>9187205.044749036</v>
       </c>
     </row>
     <row r="24">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>4870449.064339399</v>
+        <v>4772574.049220279</v>
       </c>
     </row>
     <row r="25">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>24919652.63769254</v>
+        <v>24418875.12283556</v>
       </c>
     </row>
     <row r="27">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>10619202.44328134</v>
+        <v>10405802.28531662</v>
       </c>
     </row>
     <row r="28">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>16832.27196635697</v>
+        <v>16494.01591410528</v>
       </c>
     </row>
     <row r="32">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>8065.463650546046</v>
+        <v>7903.382625508781</v>
       </c>
     </row>
     <row r="33">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>8766.808315810922</v>
+        <v>8590.6332885965</v>
       </c>
     </row>
     <row r="34">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>2281.25</v>
+        <v>2281.250000000001</v>
       </c>
     </row>
     <row r="35">
@@ -868,16 +868,16 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>17179</v>
+        <v>17182</v>
       </c>
       <c r="C2" s="11" t="n">
         <v>110267</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>930</v>
+        <v>911</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2121077</v>
+        <v>2078452</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>2281</v>
@@ -899,10 +899,10 @@
         <v>110263</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>5611</v>
+        <v>5499</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>12801188</v>
+        <v>12543940</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>2281</v>
@@ -924,10 +924,10 @@
         <v>110317</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>4962</v>
+        <v>4862</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>11319157</v>
+        <v>11091691</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>2281</v>
@@ -949,10 +949,10 @@
         <v>110231</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>3397</v>
+        <v>3329</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>7749476</v>
+        <v>7593745</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>2281</v>
@@ -968,16 +968,16 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>334087</v>
+        <v>334084</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>110343</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>1932</v>
+        <v>1893</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>4407722</v>
+        <v>4319145</v>
       </c>
       <c r="F6" s="11" t="n">
         <v>2281</v>
@@ -1047,19 +1047,19 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>8303727</v>
+        <v>8136858</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>2616243</v>
+        <v>2563667</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>5687484</v>
+        <v>5573190</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2812295</v>
+        <v>2755780</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>3640</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="3">
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>25363059</v>
+        <v>24853371</v>
       </c>
       <c r="C3" s="11" t="n">
-        <v>7991101</v>
+        <v>7830514</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>17371958</v>
+        <v>17022857</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>4736718</v>
+        <v>4641530</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>11118</v>
+        <v>10895</v>
       </c>
     </row>
     <row r="4">
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>2741393</v>
+        <v>2686303</v>
       </c>
       <c r="C4" s="11" t="n">
-        <v>863727</v>
+        <v>846369</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>1877667</v>
+        <v>1839934</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>1580519</v>
+        <v>1548757</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>1202</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="5">
@@ -1113,19 +1113,19 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>1990442</v>
+        <v>1950443</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>627126</v>
+        <v>614523</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>1363316</v>
+        <v>1335920</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>980027</v>
+        <v>960333</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>873</v>
+        <v>855</v>
       </c>
     </row>
   </sheetData>
@@ -1255,34 +1255,34 @@
         <v>4500</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>38398620</v>
+        <v>37626974</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>12098195</v>
+        <v>11855074</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>26300425</v>
+        <v>25771900</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>3071890</v>
+        <v>3010158</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>41470510</v>
+        <v>40637132</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>23039374</v>
+        <v>22576382</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>48957704</v>
+        <v>47973866</v>
       </c>
       <c r="L3" s="11" t="n">
-        <v>16832</v>
+        <v>16494</v>
       </c>
       <c r="M3" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="N3" s="11" t="n">
-        <v>15928804</v>
+        <v>15608703</v>
       </c>
     </row>
     <row r="4">
@@ -1303,34 +1303,34 @@
         <v>4500</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>63739402</v>
+        <v>62458515</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>20082277</v>
+        <v>19678710</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>43657125</v>
+        <v>42779805</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>5099152</v>
+        <v>4996681</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>68838555</v>
+        <v>67455197</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>38243976</v>
+        <v>37475437</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>81266847</v>
+        <v>79633734</v>
       </c>
       <c r="L4" s="11" t="n">
-        <v>27941</v>
+        <v>27379</v>
       </c>
       <c r="M4" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="N4" s="11" t="n">
-        <v>26440857</v>
+        <v>25909510</v>
       </c>
     </row>
     <row r="5">
@@ -1351,34 +1351,34 @@
         <v>7500</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>107396527</v>
+        <v>105238320</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>20082277</v>
+        <v>19678710</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>87314250</v>
+        <v>85559610</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>8591722</v>
+        <v>8419066</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>115988249</v>
+        <v>113657386</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>64438250</v>
+        <v>63143320</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>136929681</v>
+        <v>134177985</v>
       </c>
       <c r="L5" s="11" t="n">
-        <v>27941</v>
+        <v>27379</v>
       </c>
       <c r="M5" s="11" t="n">
         <v>3844</v>
       </c>
       <c r="N5" s="11" t="n">
-        <v>29270485</v>
+        <v>28682275</v>
       </c>
     </row>
   </sheetData>
@@ -1453,19 +1453,19 @@
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>8303727</v>
+        <v>8136858</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2616243</v>
+        <v>2563667</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>5687484</v>
+        <v>5573190</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2812295</v>
+        <v>2755780</v>
       </c>
       <c r="G2" s="11" t="n">
-        <v>3640</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="3">
@@ -1480,19 +1480,19 @@
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>25363059</v>
+        <v>24853371</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>7991101</v>
+        <v>7830514</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>17371958</v>
+        <v>17022857</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>4736718</v>
+        <v>4641530</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>11118</v>
+        <v>10895</v>
       </c>
     </row>
     <row r="4">
@@ -1507,19 +1507,19 @@
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2741393</v>
+        <v>2686303</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>863727</v>
+        <v>846369</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>1877667</v>
+        <v>1839934</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>1580519</v>
+        <v>1548757</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>1202</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="5">
@@ -1534,19 +1534,19 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>1990442</v>
+        <v>1950443</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>627126</v>
+        <v>614523</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>1363316</v>
+        <v>1335920</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>980027</v>
+        <v>960333</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>873</v>
+        <v>855</v>
       </c>
     </row>
     <row r="6">
@@ -1561,19 +1561,19 @@
         </is>
       </c>
       <c r="C6" s="11" t="n">
-        <v>8303727</v>
+        <v>8136858</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>2616243</v>
+        <v>2563667</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>5687484</v>
+        <v>5573190</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>2812295</v>
+        <v>2755780</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>3640</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="7">
@@ -1588,19 +1588,19 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>45632119</v>
+        <v>44715110</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>14377243</v>
+        <v>14088322</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>31254876</v>
+        <v>30626788</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>7067273</v>
+        <v>6925251</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>20003</v>
+        <v>19601</v>
       </c>
     </row>
     <row r="8">
@@ -1615,19 +1615,19 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>2741393</v>
+        <v>2686303</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>863727</v>
+        <v>846369</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>1877667</v>
+        <v>1839934</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>1580519</v>
+        <v>1548757</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>1202</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="9">
@@ -1642,19 +1642,19 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>7062164</v>
+        <v>6920245</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>2225065</v>
+        <v>2180351</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>4837098</v>
+        <v>4739894</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>3571707</v>
+        <v>3499931</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>3096</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="10">
@@ -1669,19 +1669,19 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>13991211</v>
+        <v>13710048</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>2616243</v>
+        <v>2563667</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>11374968</v>
+        <v>11146380</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>4738524</v>
+        <v>4643300</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>3640</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="11">
@@ -1696,19 +1696,19 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>76886995</v>
+        <v>75341898</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>14377243</v>
+        <v>14088322</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>62509752</v>
+        <v>61253575</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>11907870</v>
+        <v>11668574</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>20003</v>
+        <v>19601</v>
       </c>
     </row>
     <row r="12">
@@ -1723,19 +1723,19 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>4619060</v>
+        <v>4526237</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>863727</v>
+        <v>846369</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>3755333</v>
+        <v>3679867</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>2663065</v>
+        <v>2609549</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>1202</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="13">
@@ -1750,19 +1750,19 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>11899262</v>
+        <v>11660138</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>2225065</v>
+        <v>2180351</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>9674197</v>
+        <v>9479787</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>6018081</v>
+        <v>5897144</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>3096</v>
+        <v>3034</v>
       </c>
     </row>
   </sheetData>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12,755 -&gt; 14,126</t>
+          <t>12,755 -&gt; 13,842</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2080,7 +2080,7 @@
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>Both arms are driven by OBSERVED births — the count of age-0 dependents in each PUMS tax unit (an infant &lt;1yr ≈ a birth in the last 12 months, the annual flow). The weighted count is calibrated to CDC NVSR resident births (by-residence basis, 2022=15,535), then projected to 2028 with the repo's damped-trend ensemble (point 14,126, 90% PI [12,868, 15,384]). NVSR finals run through 2024; later years are nowcast from Hawaiʻi DOH preliminary births (snapshot 2026-07-06) converted occurrence→residence at ÷1.0026 (sd 0.0007, carried into their MOEs): 2025≈14,541; 2026≈14,416 (annualised from 5mo). Each birth draws one prenatal + one postnatal payment. This replaces the legacy num_dependents × rate proxy, which multiplied an all-dependents count (incl. older children, students, adult dependents) by a children-only-calibrated rate and overstated total births ~1.7×. County split: recalibrated to CDC WONDER county-of-RESIDENCE natality shares (2020-2024), not raw PUMS county shares — PUMS's own county allocation is small-sample-noisy (Hawaii County carries only ~11 sampled infants) and Maui/Kauai are not independently sampled at all (one combined PUMA, split by a demographic-heuristic imputer, not survey evidence). Residence basis matters here: DOH's occurrence counts overstate Honolulu ~2.2pp because neighbour-island mothers deliver on Oʻahu. Per-county factor vs the raw PUMS-implied count: Honolulu×0.92; Hawaii×1.53; Maui×1.15; Kauai×0.97. The state BIRTH total is unchanged (redistribution only), but the state COST total is NOT — eligibility is unit-specific and correlated with county, so this also corrects the eligible share (eligible_families itself is unchanged). --no-county-share-calibration restores raw PUMS shares. Cost = the take-up-adjusted benefit weighted by the household (WGTP) weight, summed to SPM-unit grain. Per-unit amounts are expectations, not literal payments.</t>
+          <t>Both arms are driven by OBSERVED births — the count of age-0 dependents in each PUMS tax unit (an infant &lt;1yr ≈ a birth in the last 12 months, the annual flow). The weighted count is calibrated to CDC NVSR resident births (by-residence basis, 2022=15,535), then projected to 2028 with the repo's damped-trend ensemble (point 13,842, 90% PI [12,779, 14,905]). NVSR finals run through 2024; later years are nowcast from Hawaiʻi DOH preliminary births (snapshot 2026-07-06) converted occurrence→residence at ÷1.0026 (sd 0.0007, carried into their MOEs): 2025≈14,541; 2026≈14,416 (annualised from 5mo). Each birth draws one prenatal + one postnatal payment. This replaces the legacy num_dependents × rate proxy, which multiplied an all-dependents count (incl. older children, students, adult dependents) by a children-only-calibrated rate and overstated total births ~1.7×. County split: recalibrated to CDC WONDER county-of-RESIDENCE natality shares (2020-2024), not raw PUMS county shares — PUMS's own county allocation is small-sample-noisy (Hawaii County carries only ~11 sampled infants) and Maui/Kauai are not independently sampled at all (one combined PUMA, split by a demographic-heuristic imputer, not survey evidence). Residence basis matters here: DOH's occurrence counts overstate Honolulu ~2.2pp because neighbour-island mothers deliver on Oʻahu. Per-county factor vs the raw PUMS-implied count: Honolulu×0.92; Hawaii×1.53; Maui×1.15; Kauai×0.97. The state BIRTH total is unchanged (redistribution only), but the state COST total is NOT — eligibility is unit-specific and correlated with county, so this also corrects the eligible share (eligible_families itself is unchanged). --no-county-share-calibration restores raw PUMS shares. Cost = the take-up-adjusted benefit weighted by the household (WGTP) weight, summed to SPM-unit grain. Per-unit amounts are expectations, not literal payments.</t>
         </is>
       </c>
     </row>

--- a/reports/rxkids_2028_flint/rxkids_2028_cost_and_impact.xlsx
+++ b/reports/rxkids_2028_flint/rxkids_2028_cost_and_impact.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>37626973.80405268</v>
+        <v>24741023.87115792</v>
       </c>
     </row>
     <row r="6">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>25771899.8657895</v>
+        <v>12885949.93289475</v>
       </c>
     </row>
     <row r="8">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>3010157.904324214</v>
+        <v>1979281.909692634</v>
       </c>
     </row>
     <row r="9">
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>40637131.70837689</v>
+        <v>26720305.78085056</v>
       </c>
     </row>
     <row r="10">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>28597198.2190936</v>
+        <v>18803637.18515743</v>
       </c>
     </row>
     <row r="11">
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>46656749.38901176</v>
+        <v>30678410.55715841</v>
       </c>
     </row>
     <row r="12">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>5489225.279610383</v>
+        <v>3609353.608510938</v>
       </c>
     </row>
     <row r="13">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>22576381.51635915</v>
+        <v>14844811.5566223</v>
       </c>
     </row>
     <row r="14">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>47973865.64302704</v>
+        <v>31544279.47858624</v>
       </c>
     </row>
     <row r="15">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>25771899.8657895</v>
+        <v>38657849.79868426</v>
       </c>
     </row>
     <row r="18">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>15608703.42797492</v>
+        <v>12357387.35694361</v>
       </c>
     </row>
     <row r="22">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>9187205.044749036</v>
+        <v>5935888.973717722</v>
       </c>
     </row>
     <row r="24">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>4772574.049220279</v>
+        <v>1044000.573266936</v>
       </c>
     </row>
     <row r="25">
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>41.5</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="26">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>24418875.12283556</v>
+        <v>18512814.73692546</v>
       </c>
     </row>
     <row r="27">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>10405802.28531662</v>
+        <v>8238258.237962404</v>
       </c>
     </row>
     <row r="28">
@@ -744,58 +744,68 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Eligible families (weighted)</t>
+          <t>Births served / year (people affected)</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>7340</v>
+        <v>8765.952335302551</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
+          <t>Eligible families (weighted)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>7340</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>Expected recipients / year</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B32" s="6" t="n">
         <v>16494.01591410528</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Expected pregnancies (prenatal)</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n">
-        <v>7903.382625508781</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Expected pregnancies (prenatal)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>7903.382625508781</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Expected infants (postnatal)</t>
         </is>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B34" s="6" t="n">
         <v>8590.6332885965</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>Avg benefit per recipient</t>
         </is>
       </c>
-      <c r="B34" s="6" t="n">
-        <v>2281.250000000001</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr"/>
+      <c r="B35" s="6" t="n">
+        <v>1500</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Benefits by income quintile → see the 'By income quintile' tab.</t>
         </is>
@@ -877,10 +887,10 @@
         <v>911</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2078452</v>
+        <v>1366653</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2281</v>
+        <v>1500</v>
       </c>
       <c r="G2" s="12" t="n">
         <v>5.5</v>
@@ -893,7 +903,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>57026</v>
+        <v>57024</v>
       </c>
       <c r="C3" s="11" t="n">
         <v>110263</v>
@@ -902,10 +912,10 @@
         <v>5499</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>12543940</v>
+        <v>8248070</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>2281</v>
+        <v>1500</v>
       </c>
       <c r="G3" s="12" t="n">
         <v>33.3</v>
@@ -927,10 +937,10 @@
         <v>4862</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>11091691</v>
+        <v>7293167</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>2281</v>
+        <v>1500</v>
       </c>
       <c r="G4" s="12" t="n">
         <v>29.5</v>
@@ -952,10 +962,10 @@
         <v>3329</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>7593745</v>
+        <v>4993148</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2281</v>
+        <v>1500</v>
       </c>
       <c r="G5" s="12" t="n">
         <v>20.2</v>
@@ -977,10 +987,10 @@
         <v>1893</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>4319145</v>
+        <v>2839986</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>2281</v>
+        <v>1500</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>11.5</v>
@@ -1047,16 +1057,16 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>8136858</v>
+        <v>5350262</v>
       </c>
       <c r="C2" s="11" t="n">
         <v>2563667</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>5573190</v>
+        <v>2786595</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>2755780</v>
+        <v>1812020</v>
       </c>
       <c r="F2" s="11" t="n">
         <v>3567</v>
@@ -1069,16 +1079,16 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>24853371</v>
+        <v>16341942</v>
       </c>
       <c r="C3" s="11" t="n">
         <v>7830514</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>17022857</v>
+        <v>8511428</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>4641530</v>
+        <v>3051965</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>10895</v>
@@ -1091,16 +1101,16 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>2686303</v>
+        <v>1766336</v>
       </c>
       <c r="C4" s="11" t="n">
         <v>846369</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>1839934</v>
+        <v>919967</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>1548757</v>
+        <v>1018361</v>
       </c>
       <c r="F4" s="11" t="n">
         <v>1178</v>
@@ -1113,16 +1123,16 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>1950443</v>
+        <v>1282483</v>
       </c>
       <c r="C5" s="11" t="n">
         <v>614523</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>1335920</v>
+        <v>667960</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>960333</v>
+        <v>631452</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>855</v>
@@ -1139,7 +1149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1240,60 +1250,60 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
+          <t>Statutory (Medicaid OR &lt;=300% FPL) - 3-mo postnatal</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Medicaid OR ≤300% FPL</t>
+          <t>Medicaid OR &lt;=300% FPL</t>
         </is>
       </c>
       <c r="C3" s="10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D3" s="11" t="n">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>37626974</v>
+        <v>24741024</v>
       </c>
       <c r="F3" s="11" t="n">
         <v>11855074</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>25771900</v>
+        <v>12885950</v>
       </c>
       <c r="H3" s="11" t="n">
-        <v>3010158</v>
+        <v>1979282</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>40637132</v>
+        <v>26720306</v>
       </c>
       <c r="J3" s="11" t="n">
-        <v>22576382</v>
+        <v>14844812</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>47973866</v>
+        <v>31544279</v>
       </c>
       <c r="L3" s="11" t="n">
         <v>16494</v>
       </c>
       <c r="M3" s="11" t="n">
-        <v>2281</v>
+        <v>1500</v>
       </c>
       <c r="N3" s="11" t="n">
-        <v>15608703</v>
+        <v>12357387</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>Universal · 6-mo postnatal</t>
+          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>Universal (no income/Medicaid test)</t>
+          <t>Medicaid OR ≤300% FPL</t>
         </is>
       </c>
       <c r="C4" s="10" t="n">
@@ -1303,40 +1313,40 @@
         <v>4500</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>62458515</v>
+        <v>37626974</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>19678710</v>
+        <v>11855074</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>42779805</v>
+        <v>25771900</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>4996681</v>
+        <v>3010158</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>67455197</v>
+        <v>40637132</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>37475437</v>
+        <v>22576382</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>79633734</v>
+        <v>47973866</v>
       </c>
       <c r="L4" s="11" t="n">
-        <v>27379</v>
+        <v>16494</v>
       </c>
       <c r="M4" s="11" t="n">
         <v>2281</v>
       </c>
       <c r="N4" s="11" t="n">
-        <v>25909510</v>
+        <v>15608703</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Universal · 12-mo postnatal</t>
+          <t>Universal · 6-mo postnatal</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -1345,39 +1355,87 @@
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>7500</v>
+        <v>4500</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>105238320</v>
+        <v>62458515</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>19678710</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>85559610</v>
+        <v>42779805</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>8419066</v>
+        <v>4996681</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>113657386</v>
+        <v>67455197</v>
       </c>
       <c r="J5" s="11" t="n">
-        <v>63143320</v>
+        <v>37475437</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>134177985</v>
+        <v>79633734</v>
       </c>
       <c r="L5" s="11" t="n">
         <v>27379</v>
       </c>
       <c r="M5" s="11" t="n">
+        <v>2281</v>
+      </c>
+      <c r="N5" s="11" t="n">
+        <v>25909510</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 12-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Universal (no income/Medicaid test)</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>105238320</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>19678710</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>85559610</v>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>8419066</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>113657386</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>63143320</v>
+      </c>
+      <c r="K6" s="11" t="n">
+        <v>134177985</v>
+      </c>
+      <c r="L6" s="11" t="n">
+        <v>27379</v>
+      </c>
+      <c r="M6" s="11" t="n">
         <v>3844</v>
       </c>
-      <c r="N5" s="11" t="n">
+      <c r="N6" s="11" t="n">
         <v>28682275</v>
       </c>
     </row>
@@ -1392,7 +1450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1444,7 +1502,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
+          <t>Statutory (Medicaid OR &lt;=300% FPL) - 3-mo postnatal</t>
         </is>
       </c>
       <c r="B2" s="10" t="inlineStr">
@@ -1453,16 +1511,16 @@
         </is>
       </c>
       <c r="C2" s="11" t="n">
-        <v>8136858</v>
+        <v>5350262</v>
       </c>
       <c r="D2" s="11" t="n">
         <v>2563667</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>5573190</v>
+        <v>2786595</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>2755780</v>
+        <v>1812020</v>
       </c>
       <c r="G2" s="11" t="n">
         <v>3567</v>
@@ -1471,7 +1529,7 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
+          <t>Statutory (Medicaid OR &lt;=300% FPL) - 3-mo postnatal</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
@@ -1480,16 +1538,16 @@
         </is>
       </c>
       <c r="C3" s="11" t="n">
-        <v>24853371</v>
+        <v>16341942</v>
       </c>
       <c r="D3" s="11" t="n">
         <v>7830514</v>
       </c>
       <c r="E3" s="11" t="n">
-        <v>17022857</v>
+        <v>8511428</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>4641530</v>
+        <v>3051965</v>
       </c>
       <c r="G3" s="11" t="n">
         <v>10895</v>
@@ -1498,7 +1556,7 @@
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
+          <t>Statutory (Medicaid OR &lt;=300% FPL) - 3-mo postnatal</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
@@ -1507,16 +1565,16 @@
         </is>
       </c>
       <c r="C4" s="11" t="n">
-        <v>2686303</v>
+        <v>1766336</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>846369</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>1839934</v>
+        <v>919967</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>1548757</v>
+        <v>1018361</v>
       </c>
       <c r="G4" s="11" t="n">
         <v>1178</v>
@@ -1525,7 +1583,7 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
+          <t>Statutory (Medicaid OR &lt;=300% FPL) - 3-mo postnatal</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -1534,16 +1592,16 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>1950443</v>
+        <v>1282483</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>614523</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>1335920</v>
+        <v>667960</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>960333</v>
+        <v>631452</v>
       </c>
       <c r="G5" s="11" t="n">
         <v>855</v>
@@ -1552,7 +1610,7 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Universal · 6-mo postnatal</t>
+          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -1579,7 +1637,7 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Universal · 6-mo postnatal</t>
+          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -1588,25 +1646,25 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>44715110</v>
+        <v>24853371</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>14088322</v>
+        <v>7830514</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>30626788</v>
+        <v>17022857</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>6925251</v>
+        <v>4641530</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>19601</v>
+        <v>10895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Universal · 6-mo postnatal</t>
+          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -1633,7 +1691,7 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Universal · 6-mo postnatal</t>
+          <t>Statutory (Medicaid OR ≤300% FPL) · 6-mo postnatal</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -1642,25 +1700,25 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>6920245</v>
+        <v>1950443</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>2180351</v>
+        <v>614523</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>4739894</v>
+        <v>1335920</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>3499931</v>
+        <v>960333</v>
       </c>
       <c r="G9" s="11" t="n">
-        <v>3034</v>
+        <v>855</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Universal · 12-mo postnatal</t>
+          <t>Universal · 6-mo postnatal</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
@@ -1669,16 +1727,16 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>13710048</v>
+        <v>8136858</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>2563667</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>11146380</v>
+        <v>5573190</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>4643300</v>
+        <v>2755780</v>
       </c>
       <c r="G10" s="11" t="n">
         <v>3567</v>
@@ -1687,7 +1745,7 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Universal · 12-mo postnatal</t>
+          <t>Universal · 6-mo postnatal</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -1696,16 +1754,16 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>75341898</v>
+        <v>44715110</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>14088322</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>61253575</v>
+        <v>30626788</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>11668574</v>
+        <v>6925251</v>
       </c>
       <c r="G11" s="11" t="n">
         <v>19601</v>
@@ -1714,7 +1772,7 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Universal · 12-mo postnatal</t>
+          <t>Universal · 6-mo postnatal</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
@@ -1723,16 +1781,16 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>4526237</v>
+        <v>2686303</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>846369</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>3679867</v>
+        <v>1839934</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>2609549</v>
+        <v>1548757</v>
       </c>
       <c r="G12" s="11" t="n">
         <v>1178</v>
@@ -1741,7 +1799,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Universal · 12-mo postnatal</t>
+          <t>Universal · 6-mo postnatal</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -1750,18 +1808,126 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>11660138</v>
+        <v>6920245</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>2180351</v>
       </c>
       <c r="E13" s="11" t="n">
+        <v>4739894</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>3499931</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>3034</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 12-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>13710048</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>2563667</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>11146380</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>4643300</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>3567</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 12-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Honolulu</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>75341898</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>14088322</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>61253575</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>11668574</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>19601</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 12-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Kauai</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>4526237</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>846369</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>3679867</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>2609549</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Universal · 12-mo postnatal</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Maui</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>11660138</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>2180351</v>
+      </c>
+      <c r="E17" s="11" t="n">
         <v>9479787</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F17" s="11" t="n">
         <v>5897144</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="G17" s="11" t="n">
         <v>3034</v>
       </c>
     </row>
